--- a/Assets/GameData/Dialogs.xlsx
+++ b/Assets/GameData/Dialogs.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\系统\文档\GitHub\VR_Zoo\Assets\GameData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4A19557-060E-4F76-A965-EE780827794A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74212445-35BF-499D-9C31-E4950E84C354}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Characters" sheetId="2" r:id="rId1"/>
-    <sheet name="Scene3" sheetId="1" r:id="rId2"/>
+    <sheet name="Scene0" sheetId="5" r:id="rId2"/>
+    <sheet name="Scene1" sheetId="7" r:id="rId3"/>
+    <sheet name="Scene2" sheetId="4" r:id="rId4"/>
+    <sheet name="Scene3" sheetId="1" r:id="rId5"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -26,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="27">
   <si>
     <t>name</t>
   </si>
@@ -54,18 +57,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>诺亚</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>将射线瞄准渡渡鸟，拇指食指捏合，抓住它！</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>test</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>characterName</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -82,15 +73,72 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>nuoya</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <t>spriteName</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>诺诺</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>nuonuo</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UI.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>胖胖</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pangpang</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>嗨~ 终于等到你啦！欢迎来到云端动物园，我是这里的向导，诺诺。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>我是胖胖！你就是今天的星光使者吧？邀请函都飞到你手里啦！</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>今晚是动物园一年一度的“星光仪式”，不过……出了点状况，需要你来帮忙。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>你看！星光轨迹上一共三站：毛里求斯沙滩、冰川秘境，最后到恐龙谷！每站各有一样东西要寻找：果实、旋律、能量。集齐这三样，仪式才能开始。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>是的，时间不等人，大家快带上邀请函，星光专列，马上发车咯！</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>渡渡鸟酋长</t>
+  </si>
+  <si>
+    <t>dodochief</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>咕咕！你可以来帮我们摘果子吗？我们……飞不上去。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>说起来，我们祖先本来会飞的。后来嘛…岛上没有天敌…不需要飞，翅膀就慢慢小了，身子慢慢圆了。</t>
+  </si>
+  <si>
+    <t>但果子还是要摘的。今晚的盛典不能没有它。</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -100,6 +148,21 @@
     </font>
     <font>
       <sz val="9"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
       <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
@@ -126,7 +189,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -136,6 +199,18 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -417,39 +492,68 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9BC0DE0-BFDC-4291-95D0-1578AA7C2A70}">
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="15" style="1" customWidth="1"/>
-    <col min="3" max="3" width="14.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15" style="1" customWidth="1"/>
+    <col min="2" max="2" width="14.109375" style="1" customWidth="1"/>
+    <col min="3" max="4" width="15" style="1" customWidth="1"/>
+    <col min="5" max="5" width="11.88671875" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E1" s="1"/>
+      <c r="E1" s="1" t="s">
+        <v>9</v>
+      </c>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K1" s="1"/>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>14</v>
       </c>
     </row>
@@ -460,6 +564,311 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B006E54E-94FC-46E9-B422-25854D8CFFE6}">
+  <dimension ref="A1:L24"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="8.88671875" style="5"/>
+    <col min="2" max="2" width="15" style="5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15" style="5" customWidth="1"/>
+    <col min="4" max="4" width="45.77734375" style="5" customWidth="1"/>
+    <col min="5" max="5" width="8.88671875" style="5"/>
+    <col min="6" max="6" width="10.21875" style="5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.33203125" style="5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.88671875" style="5" bestFit="1" customWidth="1"/>
+    <col min="9" max="16384" width="8.88671875" style="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="5"/>
+      <c r="J1" s="5"/>
+      <c r="K1" s="5"/>
+      <c r="L1" s="5"/>
+    </row>
+    <row r="2" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="4"/>
+      <c r="B2" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="4"/>
+      <c r="H2" s="4"/>
+    </row>
+    <row r="3" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="4"/>
+      <c r="B3" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
+      <c r="G3" s="4"/>
+      <c r="H3" s="4"/>
+    </row>
+    <row r="4" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="4"/>
+      <c r="B4" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+    </row>
+    <row r="5" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="4"/>
+      <c r="B5" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4"/>
+    </row>
+    <row r="6" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="8" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="18" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="19" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="20" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="21" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="22" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="23" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="24" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD1F940C-4730-4F89-8176-855EE6572F8A}">
+  <dimension ref="A1:L24"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="8.88671875" style="5"/>
+    <col min="2" max="2" width="15" style="5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15" style="5" customWidth="1"/>
+    <col min="4" max="4" width="45.77734375" style="5" customWidth="1"/>
+    <col min="5" max="5" width="8.88671875" style="5"/>
+    <col min="6" max="6" width="10.21875" style="5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.33203125" style="5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.88671875" style="5" bestFit="1" customWidth="1"/>
+    <col min="9" max="16384" width="8.88671875" style="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="5"/>
+      <c r="J1" s="5"/>
+      <c r="K1" s="5"/>
+      <c r="L1" s="5"/>
+    </row>
+    <row r="2" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="8" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17" s="5" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="18" s="5" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="19" s="5" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="20" s="5" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="21" s="5" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="22" s="5" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="23" s="5" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="24" s="5" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25"/>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33F9B2A4-6485-4016-91D5-C9EAE9B2965F}">
+  <dimension ref="A1:L24"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="8.88671875" style="2"/>
+    <col min="2" max="2" width="15" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15" style="2" customWidth="1"/>
+    <col min="4" max="4" width="30.77734375" style="2" customWidth="1"/>
+    <col min="5" max="5" width="8.88671875" style="2"/>
+    <col min="6" max="6" width="10.21875" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.33203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.88671875" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="16384" width="8.88671875" style="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
+    </row>
+    <row r="2" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="8" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="18" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="19" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="20" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="21" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="22" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="23" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="24" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L24"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
@@ -483,7 +892,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>2</v>
@@ -505,17 +914,7 @@
       <c r="K1" s="2"/>
       <c r="L1" s="2"/>
     </row>
-    <row r="2" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
+    <row r="2" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="3" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="5" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>

--- a/Assets/GameData/Dialogs.xlsx
+++ b/Assets/GameData/Dialogs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\系统\文档\GitHub\VR_Zoo\Assets\GameData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74212445-35BF-499D-9C31-E4950E84C354}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC488E03-9599-4D4B-A374-E1255BBC4E97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="29">
   <si>
     <t>name</t>
   </si>
@@ -132,6 +132,12 @@
   </si>
   <si>
     <t>但果子还是要摘的。今晚的盛典不能没有它。</t>
+  </si>
+  <si>
+    <t>太棒了！成功获取星光果实！渡渡鸟们，盛典上见！</t>
+  </si>
+  <si>
+    <t>那我们先走啦，列车还在等着呢！</t>
   </si>
 </sst>
 </file>
@@ -767,8 +773,22 @@
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="6" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>28</v>
+      </c>
+    </row>
     <row r="7" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="8" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="9" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25"/>

--- a/Assets/GameData/Dialogs.xlsx
+++ b/Assets/GameData/Dialogs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\系统\文档\GitHub\VR_Zoo\Assets\GameData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC488E03-9599-4D4B-A374-E1255BBC4E97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEF83131-25B3-4A79-9D74-F1549626A50C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Characters" sheetId="2" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="36">
   <si>
     <t>name</t>
   </si>
@@ -138,6 +138,30 @@
   </si>
   <si>
     <t>那我们先走啦，列车还在等着呢！</t>
+  </si>
+  <si>
+    <t>小翼龙</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pterosaur</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>使者~你真的来啦！我就知道我的爪印邀请函一定能找到你们！</t>
+  </si>
+  <si>
+    <t>你们快看上面！我们的翼龙大队带来了这次盛典所需的‘星光能量’。但这些能量一落到地上就会消散。我们需要你用‘提灯’把它们收集起来！</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>……每年到这一刻，我都觉得整个谷子都在屏气凝神。连最吵的副栉龙都不叫了。</t>
+  </si>
+  <si>
+    <t>我们把三样都集齐了。果实、旋律、星光。最后一步，需要你来做。</t>
+  </si>
+  <si>
+    <t>使者，你看。那里就是远古的祭坛。星光仪式的最后一步，需要你亲手去开启。</t>
   </si>
 </sst>
 </file>
@@ -498,7 +522,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9BC0DE0-BFDC-4291-95D0-1578AA7C2A70}">
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:K5"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15" style="1" customWidth="1"/>
@@ -560,6 +584,17 @@
         <v>23</v>
       </c>
       <c r="E4" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>14</v>
       </c>
     </row>
@@ -891,72 +926,107 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L24"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.88671875" style="2"/>
-    <col min="2" max="2" width="15" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15" style="2" customWidth="1"/>
-    <col min="4" max="4" width="30.77734375" style="2" customWidth="1"/>
-    <col min="5" max="5" width="8.88671875" style="2"/>
-    <col min="6" max="6" width="10.21875" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.33203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.88671875" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="16384" width="8.88671875" style="3"/>
+    <col min="1" max="1" width="8.88671875" style="4"/>
+    <col min="2" max="2" width="15" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15" style="4" customWidth="1"/>
+    <col min="4" max="4" width="45.77734375" style="4" customWidth="1"/>
+    <col min="5" max="5" width="8.88671875" style="4"/>
+    <col min="6" max="6" width="10.21875" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.33203125" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.88671875" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="16384" width="8.88671875" style="6"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-    </row>
-    <row r="2" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="6" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="7" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="9" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="10" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="11" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="12" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="15" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="18" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="19" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="20" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="21" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="22" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="23" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="24" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
+      <c r="K1" s="4"/>
+      <c r="L1" s="4"/>
+    </row>
+    <row r="2" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="8" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17" ht="45" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="18" ht="45" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="19" ht="45" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="20" ht="45" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="21" ht="45" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="22" ht="45" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="23" ht="45" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="24" ht="45" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Assets/GameData/Dialogs.xlsx
+++ b/Assets/GameData/Dialogs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\系统\文档\GitHub\VR_Zoo\Assets\GameData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEF83131-25B3-4A79-9D74-F1549626A50C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF6B6255-77AF-4BE2-96DF-2CF5F2D77869}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="37">
   <si>
     <t>name</t>
   </si>
@@ -162,6 +162,10 @@
   </si>
   <si>
     <t>使者，你看。那里就是远古的祭坛。星光仪式的最后一步，需要你亲手去开启。</t>
+  </si>
+  <si>
+    <t>小翼龙头像.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -595,7 +599,7 @@
         <v>30</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>14</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/GameData/Dialogs.xlsx
+++ b/Assets/GameData/Dialogs.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25128"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\系统\文档\GitHub\VR_Zoo\Assets\GameData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zhuangyun\Documents\GitHub\VR_Zoo\Assets\GameData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF6B6255-77AF-4BE2-96DF-2CF5F2D77869}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EDE5F8D-BCBB-4648-8CFB-FD39FB4E7676}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Characters" sheetId="2" r:id="rId1"/>
@@ -18,6 +18,7 @@
     <sheet name="Scene1" sheetId="7" r:id="rId3"/>
     <sheet name="Scene2" sheetId="4" r:id="rId4"/>
     <sheet name="Scene3" sheetId="1" r:id="rId5"/>
+    <sheet name="Scene4" sheetId="11" r:id="rId6"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -29,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="46">
   <si>
     <t>name</t>
   </si>
@@ -166,13 +167,80 @@
   <si>
     <t>小翼龙头像.png</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>小翼龙</t>
+  </si>
+  <si>
+    <t>举起提灯与魔杖，魔法的光芒会追随你的视线。瞄准星光能量，为翼龙大队照亮前路！</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>抓紧魔法梯子，抬头望向高处，然后松开双手——它会带你直达旅途的终点。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>转身向恐龙们道别，然后踏入传送门吧。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>就是这里了。你把星光能量汇进去，仪式就开始了。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>按下按钮，汇入星光能量。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>这里的每一条轨迹，都是现实世界里……对一种生命的记忆。但如果没人再记得我们，这些光……就会彻底熄灭。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>伸出你的手，射出一道星光射线，对准剪影。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="MS Mincho"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>​</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>握紧拳头——动物将化作流星，降落在你身旁。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="MS Mincho"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>​</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>它将化为半透明的灵魂，向你挥手，并讲述自己的故事。</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -201,6 +269,13 @@
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="MS Mincho"/>
+      <family val="3"/>
+      <charset val="128"/>
     </font>
   </fonts>
   <fills count="2">
@@ -999,23 +1074,172 @@
     </row>
     <row r="5" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="4" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="4" t="s">
         <v>15</v>
       </c>
+      <c r="D8" s="4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17" ht="45" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="18" ht="45" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="19" ht="45" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="20" ht="45" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="21" ht="45" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="22" ht="45" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="23" ht="45" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="24" ht="45" customHeight="1" x14ac:dyDescent="0.25"/>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E42E3FA4-6D8F-4D08-BD5D-FA1925F69587}">
+  <dimension ref="A1:L24"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="8.88671875" style="4"/>
+    <col min="2" max="2" width="15" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15" style="4" customWidth="1"/>
+    <col min="4" max="4" width="45.77734375" style="4" customWidth="1"/>
+    <col min="5" max="5" width="8.88671875" style="4"/>
+    <col min="6" max="6" width="10.21875" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.33203125" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.88671875" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="16384" width="8.88671875" style="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
+      <c r="K1" s="4"/>
+      <c r="L1" s="4"/>
+    </row>
+    <row r="2" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="F5" s="6"/>
+      <c r="G5" s="6"/>
+      <c r="H5" s="6"/>
+    </row>
+    <row r="6" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="4" t="s">
+        <v>37</v>
+      </c>
       <c r="D6" s="4" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="9" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25"/>
+        <v>45</v>
+      </c>
+      <c r="F6" s="6"/>
+      <c r="G6" s="6"/>
+      <c r="H6" s="6"/>
+    </row>
+    <row r="7" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F7" s="6"/>
+      <c r="G7" s="6"/>
+      <c r="H7" s="6"/>
+    </row>
+    <row r="8" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F8" s="6"/>
+      <c r="G8" s="6"/>
+      <c r="H8" s="6"/>
+    </row>
+    <row r="9" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F9" s="6"/>
+      <c r="G9" s="6"/>
+      <c r="H9" s="6"/>
+    </row>
     <row r="10" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="11" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="12" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25"/>

--- a/Assets/GameData/Dialogs.xlsx
+++ b/Assets/GameData/Dialogs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zhuangyun\Documents\GitHub\VR_Zoo\Assets\GameData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EDE5F8D-BCBB-4648-8CFB-FD39FB4E7676}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C341A4E-1390-48AF-8496-2058272F26C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="43">
   <si>
     <t>name</t>
   </si>
@@ -169,9 +169,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>小翼龙</t>
-  </si>
-  <si>
     <t>举起提灯与魔杖，魔法的光芒会追随你的视线。瞄准星光能量，为翼龙大队照亮前路！</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -188,59 +185,18 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>这里的每一条轨迹，都是现实世界里……对一种生命的记忆。但如果没人再记得我们，这些光……就会彻底熄灭。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>按下按钮，汇入星光能量。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>这里的每一条轨迹，都是现实世界里……对一种生命的记忆。但如果没人再记得我们，这些光……就会彻底熄灭。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>伸出你的手，射出一道星光射线，对准剪影。</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="MS Mincho"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>​</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>握紧拳头——动物将化作流星，降落在你身旁。</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="MS Mincho"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>​</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>它将化为半透明的灵魂，向你挥手，并讲述自己的故事。</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -269,13 +225,6 @@
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="MS Mincho"/>
-      <family val="3"/>
-      <charset val="128"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1077,7 +1026,7 @@
         <v>29</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25">
@@ -1093,7 +1042,7 @@
         <v>12</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25">
@@ -1109,7 +1058,7 @@
         <v>15</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -1184,7 +1133,7 @@
         <v>29</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25">
@@ -1200,27 +1149,15 @@
         <v>29</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>44</v>
-      </c>
       <c r="F5" s="6"/>
       <c r="G5" s="6"/>
       <c r="H5" s="6"/>
     </row>
     <row r="6" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>45</v>
-      </c>
       <c r="F6" s="6"/>
       <c r="G6" s="6"/>
       <c r="H6" s="6"/>
